--- a/artfynd/A 2515-2023 artfynd.xlsx
+++ b/artfynd/A 2515-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2515-2023 artfynd.xlsx
+++ b/artfynd/A 2515-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106780406</v>
+        <v>106780392</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565472.424376198</v>
+        <v>565465</v>
       </c>
       <c r="R2" t="n">
-        <v>6414249.644858757</v>
+        <v>6414243</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106780392</v>
+        <v>106780412</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,11 +813,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -852,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565464.5344363232</v>
+        <v>565471</v>
       </c>
       <c r="R3" t="n">
-        <v>6414243.131399011</v>
+        <v>6414228</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +861,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,40 +891,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106780412</v>
+        <v>106780406</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565470.6396830776</v>
+        <v>565472</v>
       </c>
       <c r="R4" t="n">
-        <v>6414228.333145074</v>
+        <v>6414250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +971,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
